--- a/public/templates/ar/impact-assessment.xlsx
+++ b/public/templates/ar/impact-assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -748,13 +748,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>ما كثافة استخدام الخدمة؟</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>منخفضة: استخدام محدود ومعاملات غير متكررة; متوسطة; مرتفعة: استخدام واسع ومعاملات متكررة</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -765,13 +765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
       </c>
       <c r="B22" t="str">
-        <v>المستوى الناتج</v>
+        <v>ما مستوى تعقيد تنفيذ الخدمة أو تحويلها؟</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>منخفض: بسيط وموحّد وقابل للتكرار; متوسط; مرتفع: متعدد الجهات ومتغيّر وخاضع لحوكمة مشددة</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
       </c>
       <c r="B23" t="str">
-        <v>الأسباب</v>
+        <v>ما مدى جاهزية الخدمة لتبنّي الذكاء الاصطناعي؟</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>منخفضة: يدوية ومجزأة وغير واضحة; متوسطة; مرتفعة: منظّمة ورقمية ومتكاملة</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>الاعتماد</v>
+        <v/>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>أعدّه</v>
+        <v>المستوى الناتج</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>راجعه</v>
+        <v>الأسباب</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>القرار</v>
+        <v>الاعتماد</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -870,21 +870,72 @@
         <v/>
       </c>
       <c r="B28" t="str">
+        <v>أعدّه</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v>راجعه</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v>القرار</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
         <v>التاريخ</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/ar/impact-assessment.xlsx
+++ b/public/templates/ar/impact-assessment.xlsx
@@ -754,7 +754,7 @@
         <v>ما كثافة استخدام الخدمة؟</v>
       </c>
       <c r="C21" t="str">
-        <v>منخفضة: استخدام محدود ومعاملات غير متكررة; متوسطة; مرتفعة: استخدام واسع ومعاملات متكررة</v>
+        <v>كثيفة: استخدام واسع ومعاملات متكررة; معتدلة; محدودة: استخدام محدود ومعاملات غير متكررة</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -771,7 +771,7 @@
         <v>ما مستوى تعقيد تنفيذ الخدمة أو تحويلها؟</v>
       </c>
       <c r="C22" t="str">
-        <v>منخفض: بسيط وموحّد وقابل للتكرار; متوسط; مرتفع: متعدد الجهات ومتغيّر وخاضع لحوكمة مشددة</v>
+        <v>بسيط: موحّد وقابل للتكرار; معقّد إلى حدٍّ ما; شديد التعقيد: متعدد الجهات ومتغيّر وخاضع لحوكمة مشددة</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -788,7 +788,7 @@
         <v>ما مدى جاهزية الخدمة لتبنّي الذكاء الاصطناعي؟</v>
       </c>
       <c r="C23" t="str">
-        <v>منخفضة: يدوية ومجزأة وغير واضحة; متوسطة; مرتفعة: منظّمة ورقمية ومتكاملة</v>
+        <v>جاهزة (رقمية ومتكاملة); جاهزة جزئياً; غير جاهزة (يدوية ومجزأة)</v>
       </c>
       <c r="D23" t="str">
         <v/>

--- a/public/templates/ar/impact-assessment.xlsx
+++ b/public/templates/ar/impact-assessment.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
+        <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B21" t="str">
         <v>ما كثافة استخدام الخدمة؟</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
+        <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B22" t="str">
         <v>ما مستوى تعقيد تنفيذ الخدمة أو تحويلها؟</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>تحديد الأولوية للذكاء الاصطناعي (اختياري)</v>
+        <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B23" t="str">
         <v>ما مدى جاهزية الخدمة لتبنّي الذكاء الاصطناعي؟</v>

--- a/public/templates/ar/impact-assessment.xlsx
+++ b/public/templates/ar/impact-assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -442,13 +442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>الفحص السريع</v>
+        <v>النطاق</v>
       </c>
       <c r="B3" t="str">
-        <v>على ماذا تؤثر مخرجات نظام الذكاء الاصطناعي؟</v>
+        <v>هل يستخدم الحل الذكاء الاصطناعي أثناء تشغيله؟</v>
       </c>
       <c r="C3" t="str">
-        <v>الإنتاجية الداخلية فقط (مسودات، ملخصات، بحث) (0); معلومات تُقدَّم للجمهور أو المتعاملين (5); توصيات للموظفين بشأن أشخاص بعينهم (15); قرارات تمس حقوق الأفراد أو مستحقاتهم أو وصولهم إلى الخدمات أو أموالهم (25); التصنيف الاجتماعي للأفراد، أو التلاعب بالسلوك، أو المراقبة البيومترية الفورية للجمهور (0)</v>
+        <v>نعم: يستخدم نموذجاً أو خدمة ذكاء اصطناعي أثناء التشغيل; لا: استُخدم الذكاء الاصطناعي في بنائه فقط، أو لم يُستخدم إطلاقاً</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -462,10 +462,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B4" t="str">
-        <v>ما البيانات التي يستخدمها؟</v>
+        <v>على ماذا تؤثر مخرجات نظام الذكاء الاصطناعي؟</v>
       </c>
       <c r="C4" t="str">
-        <v>لا بيانات عن الأشخاص، أو بيانات عامة فقط (0); بيانات عمل داخلية دون بيانات شخصية (3); بيانات شخصية (10); بيانات شخصية حساسة (18)</v>
+        <v>الإنتاجية الداخلية فقط (مسودات، ملخصات، بحث) (0); معلومات تُقدَّم للجمهور أو المتعاملين (5); توصيات للموظفين بشأن أشخاص بعينهم (15); قرارات تمس حقوق الأفراد أو مستحقاتهم أو وصولهم إلى الخدمات أو أموالهم (25); التصنيف الاجتماعي للأفراد، أو التلاعب بالسلوك، أو المراقبة البيومترية الفورية للجمهور (0)</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -479,10 +479,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B5" t="str">
-        <v>من قد يتأثر؟</v>
+        <v>ما البيانات التي يستخدمها؟</v>
       </c>
       <c r="C5" t="str">
-        <v>الموظفون فقط (3); المتعاملون أو الجمهور (8); فئات أكثر عرضة للتأثر (الأطفال، كبار السن، أصحاب الهمم) (15)</v>
+        <v>لا بيانات عن الأشخاص، أو بيانات عامة فقط (0); بيانات عمل داخلية دون بيانات شخصية (3); بيانات شخصية (10); بيانات شخصية حساسة (18)</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B6" t="str">
-        <v>ما نوع الذكاء الاصطناعي المستخدم؟</v>
+        <v>من قد يتأثر؟</v>
       </c>
       <c r="C6" t="str">
-        <v>تنبؤي (يقيّم أو يصنّف أو يتوقع) (5); توليدي (يُنتج نصوصاً أو صوراً أو إجابات) (5); وكيلي (يخطط وينفّذ إجراءات) (10)</v>
+        <v>الموظفون فقط (3); المتعاملون أو الجمهور (8); فئات أكثر عرضة للتأثر (الأطفال، كبار السن، أصحاب الهمم) (15)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B7" t="str">
-        <v>إلى أي مدى يعمل باستقلالية؟</v>
+        <v>ما نوع الذكاء الاصطناعي المستخدم؟</v>
       </c>
       <c r="C7" t="str">
-        <v>يقترح فقط؛ والإنسان يقرر وينفّذ (0); ينفّذ فقط بعد موافقة الإنسان (5); ينفّذ من تلقاء نفسه مع متابعة بشرية (15); مستقل تماماً دون تدخل بشري معتاد (25)</v>
+        <v>تنبؤي (يقيّم أو يصنّف أو يتوقع) (5); توليدي (يُنتج نصوصاً أو صوراً أو إجابات) (5); وكيلي (يخطط وينفّذ إجراءات) (10)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -530,10 +530,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B8" t="str">
-        <v>كيف يراجع البشر عمله؟</v>
+        <v>إلى أي مدى يعمل باستقلالية؟</v>
       </c>
       <c r="C8" t="str">
-        <v>يراجع شخصٌ كل مُخرج (0); مراجعة عينات أو الحالات الاستثنائية (5); فقط عند ورود شكوى (12); لا توجد مراجعة معتادة (20)</v>
+        <v>يقترح فقط؛ والإنسان يقرر وينفّذ (0); ينفّذ فقط بعد موافقة الإنسان (5); ينفّذ من تلقاء نفسه مع متابعة بشرية (15); مستقل تماماً دون تدخل بشري معتاد (25)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -547,10 +547,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B9" t="str">
-        <v>ما الذي يمكنه تغييره في الأنظمة الأخرى؟</v>
+        <v>كيف يراجع البشر عمله؟</v>
       </c>
       <c r="C9" t="str">
-        <v>لا شيء: لا صلاحيات أو قراءة فقط (0); يكتب في أدوات داخلية غير حرجة (8); يكتب في أنظمة السجل، أو يجري مدفوعات، أو يرسل رسائل خارجية (15)</v>
+        <v>يراجع شخصٌ كل مُخرج (0); مراجعة عينات أو الحالات الاستثنائية (5); فقط عند ورود شكوى (12); لا توجد مراجعة معتادة (20)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -564,10 +564,10 @@
         <v>الفحص السريع</v>
       </c>
       <c r="B10" t="str">
-        <v>إذا أخطأ، هل يمكن التراجع عن النتيجة؟</v>
+        <v>ما الذي يمكنه تغييره في الأنظمة الأخرى؟</v>
       </c>
       <c r="C10" t="str">
-        <v>نعم، بسهولة (0); نعم، ولكن بجهد (6); لا، أو فقط مع ضرر دائم (15)</v>
+        <v>لا شيء: لا صلاحيات أو قراءة فقط (0); يكتب في أدوات داخلية غير حرجة (8); يكتب في أنظمة السجل، أو يجري مدفوعات، أو يرسل رسائل خارجية (15)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -578,13 +578,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>التقييم المعمّق</v>
+        <v>الفحص السريع</v>
       </c>
       <c r="B11" t="str">
-        <v>كم عدد الأشخاص الذين يتأثرون به شهرياً؟</v>
+        <v>إذا أخطأ، هل يمكن التراجع عن النتيجة؟</v>
       </c>
       <c r="C11" t="str">
-        <v>أقل من 1,000 (0); من 1,000 إلى 100,000 (4); أكثر من 100,000 (8)</v>
+        <v>نعم، بسهولة (0); نعم، ولكن بجهد (6); لا، أو فقط مع ضرر دائم (15)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -598,10 +598,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B12" t="str">
-        <v>هل يمكنك شرح نتيجة بعينها للشخص المتأثر بها؟</v>
+        <v>كم عدد الأشخاص الذين يتأثرون به شهرياً؟</v>
       </c>
       <c r="C12" t="str">
-        <v>نعم، بلغة واضحة (0); جزئياً (4); لا (8)</v>
+        <v>أقل من 1,000 (0); من 1,000 إلى 100,000 (4); أكثر من 100,000 (8)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -615,10 +615,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B13" t="str">
-        <v>هل يعتمد على نموذج أو خدمة من طرف ثالث؟</v>
+        <v>هل يمكنك شرح نتيجة بعينها للشخص المتأثر بها؟</v>
       </c>
       <c r="C13" t="str">
-        <v>لا، مطوَّر ومستضاف داخلياً (0); نعم، مستضاف داخل الدولة وتحت سيطرتنا (3); نعم، خدمة خارجية خارج سيطرتنا (6)</v>
+        <v>نعم، بلغة واضحة (0); جزئياً (4); لا (8)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -632,10 +632,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B14" t="str">
-        <v>هل تنتقل البيانات خارج الدولة؟</v>
+        <v>هل يعتمد على نموذج أو خدمة من طرف ثالث؟</v>
       </c>
       <c r="C14" t="str">
-        <v>لا (0); غير متأكد (4); نعم (6)</v>
+        <v>لا، مطوَّر ومستضاف داخلياً (0); نعم، مستضاف داخل الدولة وتحت سيطرتنا (3); نعم، خدمة خارجية خارج سيطرتنا (6)</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -649,10 +649,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B15" t="str">
-        <v>هل اختُبر للتأكد من عدم تحيّز نتائجه بين الفئات المختلفة؟</v>
+        <v>هل تنتقل البيانات خارج الدولة؟</v>
       </c>
       <c r="C15" t="str">
-        <v>نعم، بنتائج موثّقة (0); مخطط له ولم يُنفَّذ بعد (4); لا (8)</v>
+        <v>لا (0); غير متأكد (4); نعم (6)</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -666,10 +666,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B16" t="str">
-        <v>هل اختُبر ضد إساءة الاستخدام والهجمات (مثل حقن التعليمات)؟</v>
+        <v>هل اختُبر للتأكد من عدم تحيّز نتائجه بين الفئات المختلفة؟</v>
       </c>
       <c r="C16" t="str">
-        <v>نعم (0); مخطط له (4); لا (8)</v>
+        <v>نعم، بنتائج موثّقة (0); مخطط له ولم يُنفَّذ بعد (4); لا (8)</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -683,10 +683,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B17" t="str">
-        <v>هل يُراقَب أداؤه بعد الإطلاق؟</v>
+        <v>هل اختُبر ضد إساءة الاستخدام والهجمات (مثل حقن التعليمات)؟</v>
       </c>
       <c r="C17" t="str">
-        <v>نعم، بمؤشرات ومسؤولين محددين (0); بشكل غير منتظم (4); لا (8)</v>
+        <v>نعم (0); مخطط له (4); لا (8)</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -700,10 +700,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B18" t="str">
-        <v>هل توجد آلية لإيقافه ومعالجة الحوادث؟</v>
+        <v>هل يُراقَب أداؤه بعد الإطلاق؟</v>
       </c>
       <c r="C18" t="str">
-        <v>نعم، موثّقة ومختبرة (0); جزئياً (4); لا (8)</v>
+        <v>نعم، بمؤشرات ومسؤولين محددين (0); بشكل غير منتظم (4); لا (8)</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -717,10 +717,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B19" t="str">
-        <v>هل يُستخدم في مجال خاضع للتنظيم؟</v>
+        <v>هل توجد آلية لإيقافه ومعالجة الحوادث؟</v>
       </c>
       <c r="C19" t="str">
-        <v>لا (0); نعم (6)</v>
+        <v>نعم، موثّقة ومختبرة (0); جزئياً (4); لا (8)</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -734,10 +734,10 @@
         <v>التقييم المعمّق</v>
       </c>
       <c r="B20" t="str">
-        <v>هل يُبلَّغ الأشخاص بأنهم يتعاملون مع ذكاء اصطناعي؟</v>
+        <v>هل يُستخدم في مجال خاضع للتنظيم؟</v>
       </c>
       <c r="C20" t="str">
-        <v>نعم، بوضوح (0); لا (5)</v>
+        <v>لا (0); نعم (6)</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -748,13 +748,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>تحديد الأولوية للذكاء الاصطناعي</v>
+        <v>التقييم المعمّق</v>
       </c>
       <c r="B21" t="str">
-        <v>ما كثافة استخدام الخدمة؟</v>
+        <v>هل يُبلَّغ الأشخاص بأنهم يتعاملون مع ذكاء اصطناعي؟</v>
       </c>
       <c r="C21" t="str">
-        <v>كثيفة: استخدام واسع ومعاملات متكررة; معتدلة; محدودة: استخدام محدود ومعاملات غير متكررة</v>
+        <v>نعم، بوضوح (0); لا (5)</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -768,10 +768,10 @@
         <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B22" t="str">
-        <v>ما مستوى تعقيد تنفيذ الخدمة أو تحويلها؟</v>
+        <v>ما كثافة استخدام الخدمة؟</v>
       </c>
       <c r="C22" t="str">
-        <v>بسيط: موحّد وقابل للتكرار; معقّد إلى حدٍّ ما; شديد التعقيد: متعدد الجهات ومتغيّر وخاضع لحوكمة مشددة</v>
+        <v>كثيفة: استخدام واسع ومعاملات متكررة; معتدلة; محدودة: استخدام محدود ومعاملات غير متكررة</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -785,10 +785,10 @@
         <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B23" t="str">
-        <v>ما مدى جاهزية الخدمة لتبنّي الذكاء الاصطناعي؟</v>
+        <v>ما مستوى تعقيد تنفيذ الخدمة أو تحويلها؟</v>
       </c>
       <c r="C23" t="str">
-        <v>جاهزة (رقمية ومتكاملة); جاهزة جزئياً; غير جاهزة (يدوية ومجزأة)</v>
+        <v>بسيط: موحّد وقابل للتكرار; معقّد إلى حدٍّ ما; شديد التعقيد: متعدد الجهات ومتغيّر وخاضع لحوكمة مشددة</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>تحديد الأولوية للذكاء الاصطناعي</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>ما مدى جاهزية الخدمة لتبنّي الذكاء الاصطناعي؟</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>جاهزة (رقمية ومتكاملة); جاهزة جزئياً; غير جاهزة (يدوية ومجزأة)</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>المستوى الناتج</v>
+        <v/>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>الأسباب</v>
+        <v>المستوى الناتج</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>الاعتماد</v>
+        <v>الأسباب</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -870,7 +870,7 @@
         <v/>
       </c>
       <c r="B28" t="str">
-        <v>أعدّه</v>
+        <v>الاعتماد</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v/>
       </c>
       <c r="B29" t="str">
-        <v>راجعه</v>
+        <v>أعدّه</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -904,7 +904,7 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>القرار</v>
+        <v>راجعه</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -921,21 +921,38 @@
         <v/>
       </c>
       <c r="B31" t="str">
+        <v>القرار</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
         <v>التاريخ</v>
       </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/ar/impact-assessment.xlsx
+++ b/public/templates/ar/impact-assessment.xlsx
@@ -465,7 +465,7 @@
         <v>على ماذا تؤثر مخرجات نظام الذكاء الاصطناعي؟</v>
       </c>
       <c r="C4" t="str">
-        <v>الإنتاجية الداخلية فقط (مسودات، ملخصات، بحث) (0); معلومات تُقدَّم للجمهور أو المتعاملين (5); توصيات للموظفين بشأن أشخاص بعينهم (15); قرارات تمس حقوق الأفراد أو مستحقاتهم أو وصولهم إلى الخدمات أو أموالهم (25); التصنيف الاجتماعي للأفراد، أو التلاعب بالسلوك، أو المراقبة البيومترية الفورية للجمهور (0)</v>
+        <v>الإنتاجية الداخلية فقط (مسودات، ملخصات، بحث) (0); معلومات تُقدَّم للجمهور أو المتعاملين (5); توصيات للموظفين بشأن أشخاص بعينهم (15); قرارات تمس حقوق الأفراد أو مستحقاتهم أو وصولهم إلى الخدمات أو أموالهم (25); قرارات أو مواقف عالية الأثر تخص شركات أخرى (المطالبات، والمواقف التعاقدية، والقرارات التجارية أو الائتمانية بشأن المنشآت) (20); التصنيف الاجتماعي للأفراد، أو التلاعب بالسلوك، أو المراقبة البيومترية الفورية للجمهور (0)</v>
       </c>
       <c r="D4" t="str">
         <v/>
